--- a/IRCS4_build/input_excel/input trad con.xlsx
+++ b/IRCS4_build/input_excel/input trad con.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\run control 4\input_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\13. Employee Folder\Christo\control 4\Q3 25\input excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B4BD3E-05EF-48E6-889F-B4332E12552A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6413ED-C59A-4C77-8424-752669085D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3E507947-667D-48FC-8161-25FD0280FDA7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{3E507947-667D-48FC-8161-25FD0280FDA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Filter UVSG" sheetId="5" r:id="rId5"/>
     <sheet name="Code" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="103">
   <si>
     <t>Name</t>
   </si>
@@ -70,27 +70,12 @@
     <t>UVSG File Name</t>
   </si>
   <si>
-    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-EXPNODETAILS-EOQ_20250630</t>
-  </si>
-  <si>
     <t>Data_Extraction_run142TRAD_Con</t>
   </si>
   <si>
     <t>Data_Extraction_run142UVSG</t>
   </si>
   <si>
-    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-NONECASSUMPNODETAILS-EOQ_20250630</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPEQUITYLEVEL-EOQ_20250630</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPINTLEVEL-EOQ_20250630</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPOTHERCURRENCY-EOQ_20250630</t>
-  </si>
-  <si>
     <t>Data_Extraction_run4TRAD_Con</t>
   </si>
   <si>
@@ -121,9 +106,6 @@
     <t>Data_Extraction_run40TRAD_Con</t>
   </si>
   <si>
-    <t>ID0002_AZTRAD_E_D_NB_IFRS-BE-BOQ_20250630</t>
-  </si>
-  <si>
     <t>SUM_BE</t>
   </si>
   <si>
@@ -148,9 +130,6 @@
     <t>ID0002_AZTRAD_B_D_NB_IFRS-UNWINDINGPRJCF-BOQ_20251231</t>
   </si>
   <si>
-    <t>Data_Extraction_run41TRAD_Con</t>
-  </si>
-  <si>
     <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-EXPOTHER-EOQ_20250331</t>
   </si>
   <si>
@@ -166,18 +145,12 @@
     <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-EXPOTHER-EOQ_20250930</t>
   </si>
   <si>
-    <t>Data_Extraction_run32TRAD_Con</t>
-  </si>
-  <si>
     <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-EXPOTHER-EOQ_20251231</t>
   </si>
   <si>
     <t>Data_Extraction_run42TRAD_Con</t>
   </si>
   <si>
-    <t>ID0002_AZTRAD_G_D_NB_IFRS-EXPVARIANCE-EOQ_20250630</t>
-  </si>
-  <si>
     <t>SUM_EXPOTHER</t>
   </si>
   <si>
@@ -199,154 +172,184 @@
     <t>Data_Extraction_run43TRAD_Con</t>
   </si>
   <si>
-    <t>ID0002_AZTRAD_G_D_NB_IFRS-NFA-EOQ_20250630</t>
+    <t>Data_Extraction_run4TRAD_Con - Copy</t>
+  </si>
+  <si>
+    <t>Speed Duration</t>
+  </si>
+  <si>
+    <t>Include Year</t>
+  </si>
+  <si>
+    <t>Exclude Year</t>
+  </si>
+  <si>
+    <t>File Name</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>output_path</t>
+  </si>
+  <si>
+    <t>output_filename</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Val Year</t>
+  </si>
+  <si>
+    <t>Val Month</t>
+  </si>
+  <si>
+    <t>Val Day</t>
+  </si>
+  <si>
+    <t>File naming</t>
+  </si>
+  <si>
+    <t>AZTRAD ARGO File Path</t>
+  </si>
+  <si>
+    <t>AZTRAD ARGO File Path - Old</t>
+  </si>
+  <si>
+    <t>I:\13. Employee Folder\IFRS 17\IFRS 17 Quarterly Submissions\2022\Q4\09. ARGO\CF File\AZTRAD\</t>
+  </si>
+  <si>
+    <t>AZTRAD Extract File Path</t>
+  </si>
+  <si>
+    <t>UL Extract File Path</t>
+  </si>
+  <si>
+    <t>prm_inc</t>
+  </si>
+  <si>
+    <t>lrc_cl_ins</t>
+  </si>
+  <si>
+    <t>lrc_cl_inv</t>
+  </si>
+  <si>
+    <t>r_exp_m</t>
+  </si>
+  <si>
+    <t>r_acq_cost</t>
+  </si>
+  <si>
+    <t>cov_units</t>
+  </si>
+  <si>
+    <t>dac_cov_units</t>
+  </si>
+  <si>
+    <t>dac</t>
+  </si>
+  <si>
+    <t>nattr_exp_acq</t>
+  </si>
+  <si>
+    <t>nattr_exp_inv</t>
+  </si>
+  <si>
+    <t>nattr_exp_maint</t>
+  </si>
+  <si>
+    <t>nattr_exp</t>
+  </si>
+  <si>
+    <t>c_sar</t>
+  </si>
+  <si>
+    <t>pv_r_exp_m</t>
+  </si>
+  <si>
+    <t>pv_surr</t>
+  </si>
+  <si>
+    <t>lrc_cl_ins_dth</t>
+  </si>
+  <si>
+    <t>lrc_cl_inv_dth</t>
+  </si>
+  <si>
+    <t>lrc_cl_inv_surr</t>
+  </si>
+  <si>
+    <t>lrc_cl_inv_mat</t>
+  </si>
+  <si>
+    <t>lrc_cl_inv_ann</t>
+  </si>
+  <si>
+    <t>P:\13. Employee Folder\IFRS17\2025\Q3\09. ARGO\CF File\AZTRAD\Conven\</t>
+  </si>
+  <si>
+    <t>P:\13. Employee Folder\IFRS17\2025\Q3\03. RAFM\Extraction\TRAD\Conventional\</t>
+  </si>
+  <si>
+    <t>P:\13. Employee Folder\IFRS17\2025\Q3\03. RAFM\Extraction\UVSG\</t>
+  </si>
+  <si>
+    <t>P:\13. Employee Folder\Christo\control 4\Q3 25\trad con\ARGO</t>
+  </si>
+  <si>
+    <t>P:\13. Employee Folder\Christo\control 4\Q3 25\trad con\RAFM</t>
+  </si>
+  <si>
+    <t>P:\13. Employee Folder\Christo\control 4\Q3 25\trad con\UVSG</t>
+  </si>
+  <si>
+    <t>D:\Test Run Python\IRCS4_build\RAFM MANUAL\RAFM Manual trad con.xlsx</t>
+  </si>
+  <si>
+    <t>P:\13. Employee Folder\Christo\control 4\Q3 25\trad con</t>
+  </si>
+  <si>
+    <t>trad con Q3 25.xlsx</t>
+  </si>
+  <si>
+    <t>Data_Extraction_run2TRAD_Con</t>
+  </si>
+  <si>
+    <t>Data_Extraction_run2UVSG</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-EXPNODETAILS-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-NONECASSUMPNODETAILS-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPEQUITYLEVEL-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPINTLEVEL-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPOTHERCURRENCY-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_E_D_NB_IFRS-BE-BOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_NB_IFRS-EXPVARIANCE-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_NB_IFRS-NFA-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_NB_IFRS-FA-EOQ_20250930</t>
   </si>
   <si>
     <t>SUM_NONECASSUMPOTHER</t>
   </si>
   <si>
-    <t>ID0002_AZTRAD_G_D_NB_IFRS-FA-EOQ_20250630</t>
-  </si>
-  <si>
-    <t>Data_Extraction_run4TRAD_Con - Copy</t>
-  </si>
-  <si>
-    <t>Speed Duration</t>
-  </si>
-  <si>
-    <t>Include Year</t>
-  </si>
-  <si>
-    <t>Exclude Year</t>
-  </si>
-  <si>
-    <t>File Name</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>output_path</t>
-  </si>
-  <si>
-    <t>D:\Python\run control 4\output</t>
-  </si>
-  <si>
-    <t>output_filename</t>
-  </si>
-  <si>
-    <t>trad con.xlsx</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Val Year</t>
-  </si>
-  <si>
-    <t>Val Month</t>
-  </si>
-  <si>
-    <t>Val Day</t>
-  </si>
-  <si>
-    <t>File naming</t>
-  </si>
-  <si>
-    <t>AZTRAD ARGO File Path</t>
-  </si>
-  <si>
-    <t>P:\13. Employee Folder\IFRS17\2025\Q2\09. ARGO\CF File\AZTRAD\Conven\</t>
-  </si>
-  <si>
-    <t>AZTRAD ARGO File Path - Old</t>
-  </si>
-  <si>
-    <t>I:\13. Employee Folder\IFRS 17\IFRS 17 Quarterly Submissions\2022\Q4\09. ARGO\CF File\AZTRAD\</t>
-  </si>
-  <si>
-    <t>AZTRAD Extract File Path</t>
-  </si>
-  <si>
-    <t>P:\13. Employee Folder\IFRS17\2025\Q2\03. RAFM\Extraction\TRAD\Conventional\</t>
-  </si>
-  <si>
-    <t>UL Extract File Path</t>
-  </si>
-  <si>
-    <t>P:\13. Employee Folder\IFRS17\2025\Q2\03. RAFM\Extraction\UVSG\</t>
-  </si>
-  <si>
-    <t>prm_inc</t>
-  </si>
-  <si>
-    <t>lrc_cl_ins</t>
-  </si>
-  <si>
-    <t>lrc_cl_inv</t>
-  </si>
-  <si>
-    <t>r_exp_m</t>
-  </si>
-  <si>
-    <t>r_acq_cost</t>
-  </si>
-  <si>
-    <t>cov_units</t>
-  </si>
-  <si>
-    <t>dac_cov_units</t>
-  </si>
-  <si>
-    <t>dac</t>
-  </si>
-  <si>
-    <t>nattr_exp_acq</t>
-  </si>
-  <si>
-    <t>nattr_exp_inv</t>
-  </si>
-  <si>
-    <t>nattr_exp_maint</t>
-  </si>
-  <si>
-    <t>nattr_exp</t>
-  </si>
-  <si>
-    <t>c_sar</t>
-  </si>
-  <si>
-    <t>pv_r_exp_m</t>
-  </si>
-  <si>
-    <t>pv_surr</t>
-  </si>
-  <si>
-    <t>lrc_cl_ins_dth</t>
-  </si>
-  <si>
-    <t>lrc_cl_inv_dth</t>
-  </si>
-  <si>
-    <t>lrc_cl_inv_surr</t>
-  </si>
-  <si>
-    <t>lrc_cl_inv_mat</t>
-  </si>
-  <si>
-    <t>lrc_cl_inv_ann</t>
-  </si>
-  <si>
-    <t>D:\Python\run control 4\Input\CF File\AZTRAD\Conven</t>
-  </si>
-  <si>
-    <t>D:\Python\run control 4\Input\03. RAFM\Extraction\TRAD\Conventional</t>
-  </si>
-  <si>
-    <t>D:\Python\run control 4\Input\03. RAFM\Extraction\UVSG\convent</t>
-  </si>
-  <si>
-    <t>D:\Python\run control 4\Input\RAFM MANUAL\RAFM Manual Trad Con.xlsx</t>
+    <t>C_sar</t>
   </si>
 </sst>
 </file>
@@ -404,7 +407,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -427,11 +430,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -446,6 +460,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -780,7 +795,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3533F1D-F1D9-44A7-93AE-BE7365137111}">
-  <dimension ref="A1:C9"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
@@ -789,15 +805,15 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B1" s="7">
-        <v>45809</v>
+        <v>45901</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B2" s="8">
         <v>2025</v>
@@ -805,15 +821,15 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="B3" s="8">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B4" s="8">
         <v>30</v>
@@ -821,10 +837,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="8">
-        <v>20250630</v>
+        <v>55</v>
+      </c>
+      <c r="B5" s="6">
+        <v>20250930</v>
       </c>
       <c r="C5" s="6">
         <v>20230930</v>
@@ -832,34 +848,38 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>71</v>
+        <v>56</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>73</v>
+        <v>57</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>77</v>
+        <v>59</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -870,6 +890,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50CFD0D-886E-451A-8337-46C7EB9A8542}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -878,64 +899,64 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -1007,6 +1028,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86935E8-9509-4E4E-B853-139B75EE5E09}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1027,7 +1049,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1035,7 +1057,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -1043,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -1051,23 +1073,23 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1080,376 +1102,526 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5DFDF9-BC78-4956-BABA-B2D1AE47F4C2}">
-  <dimension ref="A1:D26"/>
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D2" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D4" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D5" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>0</v>
-      </c>
-      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>0</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="B11" s="1">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>0</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>33</v>
+      <c r="B14" s="1">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>0</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>0</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>0</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>0</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>55</v>
+      <c r="B26" s="1">
+        <v>0</v>
       </c>
       <c r="C26" s="3">
         <v>2025</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="str">
+        <f>A12&amp;"_ori"</f>
+        <v>Data_Extraction_run11TRAD_azcp_Con_ori</v>
+      </c>
+      <c r="B28" s="1">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="str">
+        <f t="shared" ref="A29:A30" si="0">A13&amp;"_ori"</f>
+        <v>Data_Extraction_run21TRAD_Con_ori</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Data_Extraction_run31TRAD_Con_ori</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="str">
+        <f>A15&amp;"_ori"</f>
+        <v>_ori</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1462,215 +1634,258 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8071C82-16E8-4132-9192-2C8D7113D0E0}">
-  <dimension ref="A1:D26"/>
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D2" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D4" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D5" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3">
         <v>2025</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1682,7 +1897,8 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE40447-EFD9-4533-9619-0FD56D9BC4CA}">
-  <dimension ref="A1:C26"/>
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67" bestFit="1" customWidth="1"/>
@@ -1703,241 +1919,264 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>35</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B15" s="1"/>
       <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="str">
+        <f>B12&amp;"_ori"</f>
+        <v>Data_Extraction_run11TRAD_azcp_Con_ori</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="str">
+        <f>B13&amp;"_ori"</f>
+        <v>Data_Extraction_run21TRAD_Con_ori</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="str">
+        <f>B14&amp;"_ori"</f>
+        <v>Data_Extraction_run31TRAD_Con_ori</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="str">
+        <f>B15&amp;"_ori"</f>
+        <v>_ori</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Internal&amp;1#_x000D_</oddHeader>
   </headerFooter>

--- a/IRCS4_build/input_excel/input trad con.xlsx
+++ b/IRCS4_build/input_excel/input trad con.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\13. Employee Folder\Christo\control 4\Q3 25\input excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6413ED-C59A-4C77-8424-752669085D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9614A89-4A13-468F-B318-BA13BAF7B293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{3E507947-667D-48FC-8161-25FD0280FDA7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3E507947-667D-48FC-8161-25FD0280FDA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="103">
   <si>
     <t>Name</t>
   </si>
@@ -307,49 +307,49 @@
     <t>D:\Test Run Python\IRCS4_build\RAFM MANUAL\RAFM Manual trad con.xlsx</t>
   </si>
   <si>
-    <t>P:\13. Employee Folder\Christo\control 4\Q3 25\trad con</t>
+    <t>Data_Extraction_run2TRAD_Con</t>
+  </si>
+  <si>
+    <t>Data_Extraction_run2UVSG</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-EXPNODETAILS-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-NONECASSUMPNODETAILS-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPEQUITYLEVEL-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPINTLEVEL-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPOTHERCURRENCY-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_E_D_NB_IFRS-BE-BOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_NB_IFRS-EXPVARIANCE-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_NB_IFRS-NFA-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>ID0002_AZTRAD_G_D_NB_IFRS-FA-EOQ_20250930</t>
+  </si>
+  <si>
+    <t>SUM_NONECASSUMPOTHER</t>
+  </si>
+  <si>
+    <t>C_sar</t>
+  </si>
+  <si>
+    <t>P:\13. Employee Folder\Christo\control 4\Q3 25\Output</t>
   </si>
   <si>
     <t>trad con Q3 25.xlsx</t>
-  </si>
-  <si>
-    <t>Data_Extraction_run2TRAD_Con</t>
-  </si>
-  <si>
-    <t>Data_Extraction_run2UVSG</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-EXPNODETAILS-EOQ_20250930</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-NONECASSUMPNODETAILS-EOQ_20250930</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPEQUITYLEVEL-EOQ_20250930</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPINTLEVEL-EOQ_20250930</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_G_D_IF-IF_IFRS-ECASSUMPOTHERCURRENCY-EOQ_20250930</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_E_D_NB_IFRS-BE-BOQ_20250930</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_G_D_NB_IFRS-EXPVARIANCE-EOQ_20250930</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_G_D_NB_IFRS-NFA-EOQ_20250930</t>
-  </si>
-  <si>
-    <t>ID0002_AZTRAD_G_D_NB_IFRS-FA-EOQ_20250930</t>
-  </si>
-  <si>
-    <t>SUM_NONECASSUMPOTHER</t>
-  </si>
-  <si>
-    <t>C_sar</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1081,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1089,7 +1089,7 @@
         <v>50</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +1103,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5DFDF9-BC78-4956-BABA-B2D1AE47F4C2}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.109375" bestFit="1" customWidth="1"/>
@@ -1126,12 +1126,12 @@
         <v>46</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B25" s="1">
         <v>0</v>
@@ -1549,78 +1549,6 @@
         <v>48</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="str">
-        <f>A12&amp;"_ori"</f>
-        <v>Data_Extraction_run11TRAD_azcp_Con_ori</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="str">
-        <f t="shared" ref="A29:A30" si="0">A13&amp;"_ori"</f>
-        <v>Data_Extraction_run21TRAD_Con_ori</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Data_Extraction_run31TRAD_Con_ori</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="str">
-        <f>A15&amp;"_ori"</f>
-        <v>_ori</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1659,12 +1587,12 @@
         <v>46</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -1898,7 +1826,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE40447-EFD9-4533-9619-0FD56D9BC4CA}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67" bestFit="1" customWidth="1"/>
@@ -1919,18 +1847,18 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
@@ -1941,7 +1869,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>9</v>
@@ -1952,7 +1880,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>9</v>
@@ -1963,7 +1891,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
@@ -2010,7 +1938,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>21</v>
@@ -2089,7 +2017,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>36</v>
@@ -2134,45 +2062,21 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="3"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="str">
-        <f>B12&amp;"_ori"</f>
-        <v>Data_Extraction_run11TRAD_azcp_Con_ori</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B28" s="1" t="str">
-        <f>B13&amp;"_ori"</f>
-        <v>Data_Extraction_run21TRAD_Con_ori</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B29" s="1" t="str">
-        <f>B14&amp;"_ori"</f>
-        <v>Data_Extraction_run31TRAD_Con_ori</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="str">
-        <f>B15&amp;"_ori"</f>
-        <v>_ori</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
